--- a/src/lib/testing/fixtures/xlsx/statement.xlsx
+++ b/src/lib/testing/fixtures/xlsx/statement.xlsx
@@ -183,7 +183,7 @@
         <v>14</v>
       </c>
       <c r="E5">
-        <v>0.30000000000000004</v>
+        <v>0.3</v>
       </c>
       <c r="F5" t="s">
         <v>8</v>
